--- a/industry/input_data/steel/Worldsteel-totalproductionofcrudesteel.xlsx
+++ b/industry/input_data/steel/Worldsteel-totalproductionofcrudesteel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fraunhofer-my.sharepoint.com/personal/rakesh_etikala_narendar_iee_fraunhofer_de/Documents/Desktop/sectoral-energy-demands/industry/input_data/steel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_3352B0E1F3F105F010E720AC36A94142DD0FB1ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCA2D881-0C3A-42AA-9573-E1B07D26709E}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_3352B0E1F3F105F010E720AC36A94142DD0FB1ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA850618-9864-4111-B91A-DAB19A6736F3}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="2480" windowWidth="18630" windowHeight="15090" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="16870" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P1_crude_steel_total_pub" sheetId="1" r:id="rId1"/>
@@ -433,16 +433,18 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -468,25 +470,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -838,10 +842,11 @@
   <cols>
     <col min="1" max="1" width="37.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
@@ -849,22 +854,22 @@
       <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>2020</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>2021</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>2022</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>2023</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>2024</v>
       </c>
     </row>
@@ -872,19 +877,19 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
-        <v>0</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="B4" s="6">
+        <v>0</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
         <v>0</v>
       </c>
     </row>
@@ -892,19 +897,19 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>3000</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>3491.3240000000001</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>4300</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>4421</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>4520</v>
       </c>
     </row>
@@ -912,19 +917,19 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>250</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>275</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>270</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>190</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>285</v>
       </c>
     </row>
@@ -932,19 +937,19 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>3651.143</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>4875.0829999999996</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>5093.8689999999997</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>4928.3630000000003</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>3862.6080000000002</v>
       </c>
     </row>
@@ -952,19 +957,19 @@
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="7">
-        <v>0</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="B8" s="6">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
         <v>0</v>
       </c>
     </row>
@@ -972,19 +977,19 @@
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>5490.491</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>5779.616</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>5621.2839999999997</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>5256.2839999999997</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>4657.826</v>
       </c>
     </row>
@@ -992,19 +997,19 @@
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>6765.07</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>7884.0190000000002</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>7512.2420000000002</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>7133.13</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>7129.8720000000003</v>
       </c>
     </row>
@@ -1012,19 +1017,19 @@
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>200</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>285.714</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>359</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>349.08300000000003</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>354.82299999999998</v>
       </c>
     </row>
@@ -1032,19 +1037,19 @@
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>900</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>1167.25</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>1170.336</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>1265.5630000000001</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>1205</v>
       </c>
     </row>
@@ -1052,19 +1057,19 @@
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>4700</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>5500</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>6000</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>5000</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>4500</v>
       </c>
     </row>
@@ -1072,19 +1077,19 @@
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>2482</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>2481.3539999999998</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>2021.5</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>2300</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>2330</v>
       </c>
     </row>
@@ -1092,19 +1097,19 @@
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>6119.183</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>6909.2879999999996</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>7030.3720000000003</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <v>5863.558</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>7134.81</v>
       </c>
     </row>
@@ -1112,19 +1117,19 @@
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="7">
-        <v>0</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="B16" s="6">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1132,19 +1137,19 @@
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="7">
-        <v>0</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="B17" s="6">
+        <v>0</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1152,19 +1157,19 @@
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>759.27800000000002</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>774.83100000000002</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>653.24644999999998</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6">
         <v>582.053</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>600</v>
       </c>
     </row>
@@ -1172,19 +1177,19 @@
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <v>31414.856</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="6">
         <v>36071.067000000003</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <v>34089.495000000003</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <v>32030.174999999999</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>33880.195</v>
       </c>
     </row>
@@ -1192,19 +1197,19 @@
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6">
         <v>483.8</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="6">
         <v>547.5</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="6">
         <v>481.5</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6">
         <v>489.2</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <v>450</v>
       </c>
     </row>
@@ -1212,19 +1217,19 @@
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="7">
-        <v>0</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0</v>
-      </c>
-      <c r="F21" s="7">
+      <c r="B21" s="6">
+        <v>0</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1232,19 +1237,19 @@
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="6">
         <v>10986</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="6">
         <v>12976.29</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="6">
         <v>12097.573</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="6">
         <v>12168.092000000001</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="6">
         <v>12349.087</v>
       </c>
     </row>
@@ -1252,19 +1257,19 @@
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="6">
         <v>1157.2670000000001</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="6">
         <v>1317.5409999999999</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="6">
         <v>1150.9580000000001</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="6">
         <v>1161.777</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <v>824.154</v>
       </c>
     </row>
@@ -1272,19 +1277,19 @@
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="6">
         <v>1064766.8</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="6">
         <v>1035242.6</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="6">
         <v>1017959</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="6">
         <v>1028859.7</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="6">
         <v>1005090</v>
       </c>
     </row>
@@ -1292,19 +1297,19 @@
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
         <v>1148.9069999999999</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="6">
         <v>1338.2329999999999</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>1319.778</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="6">
         <v>1373.8689999999999</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="6">
         <v>1284.4390000000001</v>
       </c>
     </row>
@@ -1312,19 +1317,19 @@
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="7">
-        <v>0</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7">
-        <v>0</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="B26" s="6">
+        <v>0</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1332,19 +1337,19 @@
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <v>45.273000000000003</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <v>185.14400000000001</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="6">
         <v>169.13499999999999</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="6">
         <v>212.43299999999999</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>153.249</v>
       </c>
     </row>
@@ -1352,19 +1357,19 @@
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="6">
         <v>185.16399999999999</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="6">
         <v>230.84800000000001</v>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="6">
         <v>200.41399999999999</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="6">
         <v>175.38200000000001</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="6">
         <v>178.69</v>
       </c>
     </row>
@@ -1372,19 +1377,19 @@
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="7">
-        <v>0</v>
-      </c>
-      <c r="C29" s="7">
-        <v>0</v>
-      </c>
-      <c r="D29" s="7">
-        <v>0</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0</v>
-      </c>
-      <c r="F29" s="7">
+      <c r="B29" s="6">
+        <v>0</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1392,19 +1397,19 @@
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="6">
         <v>4464.634</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="6">
         <v>4817.3270000000002</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>4289.3389999999999</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="6">
         <v>3384.3180000000002</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="6">
         <v>2547.915</v>
       </c>
     </row>
@@ -1412,19 +1417,19 @@
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="6">
         <v>707</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="6">
         <v>598</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="6">
         <v>289</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="6">
         <v>347</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="6">
         <v>509</v>
       </c>
     </row>
@@ -1432,19 +1437,19 @@
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="7">
-        <v>0</v>
-      </c>
-      <c r="C32" s="7">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7">
+      <c r="B32" s="6">
+        <v>0</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1452,19 +1457,19 @@
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="7">
-        <v>0</v>
-      </c>
-      <c r="C33" s="7">
-        <v>0</v>
-      </c>
-      <c r="D33" s="7">
-        <v>0</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0</v>
-      </c>
-      <c r="F33" s="7">
+      <c r="B33" s="6">
+        <v>0</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1472,19 +1477,19 @@
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="6">
         <v>482.19200000000001</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="6">
         <v>611.63199999999995</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="6">
         <v>536.34400000000005</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="6">
         <v>484.18200000000002</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="6">
         <v>492.64400000000001</v>
       </c>
     </row>
@@ -1492,19 +1497,19 @@
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="6">
         <v>8228.6759999999995</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>10293.525</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="6">
         <v>9818.5130000000008</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="6">
         <v>10353.616</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="6">
         <v>10730.909</v>
       </c>
     </row>
@@ -1512,19 +1517,19 @@
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="6">
         <v>81.602000000000004</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="6">
         <v>102.77800000000001</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="6">
         <v>88.856999999999999</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="6">
         <v>83.611999999999995</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="6">
         <v>85.147999999999996</v>
       </c>
     </row>
@@ -1532,19 +1537,19 @@
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="7">
-        <v>0</v>
-      </c>
-      <c r="C37" s="7">
-        <v>0</v>
-      </c>
-      <c r="D37" s="7">
-        <v>0</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0</v>
-      </c>
-      <c r="F37" s="7">
+      <c r="B37" s="6">
+        <v>0</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0</v>
+      </c>
+      <c r="F37" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1552,19 +1557,19 @@
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B38" s="7">
-        <v>0</v>
-      </c>
-      <c r="C38" s="7">
-        <v>0</v>
-      </c>
-      <c r="D38" s="7">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7">
+      <c r="B38" s="6">
+        <v>0</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1572,19 +1577,19 @@
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="6">
         <v>3499</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="6">
         <v>4339</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="6">
         <v>3538.2</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="6">
         <v>3810.5</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="6">
         <v>3663.8</v>
       </c>
     </row>
@@ -1592,19 +1597,19 @@
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="7">
-        <v>0</v>
-      </c>
-      <c r="C40" s="7">
-        <v>0</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7">
+      <c r="B40" s="6">
+        <v>0</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0</v>
+      </c>
+      <c r="F40" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1612,19 +1617,19 @@
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="6">
         <v>11595.698</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="6">
         <v>13946.654</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="6">
         <v>12118.566999999999</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="6">
         <v>9996.2039999999997</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="6">
         <v>10754.986999999999</v>
       </c>
     </row>
@@ -1632,19 +1637,19 @@
       <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="6">
         <v>133.63800000000001</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="6">
         <v>135.72800000000001</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="6">
         <v>152.66900000000001</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="6">
         <v>128.398</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="6">
         <v>138.34200000000001</v>
       </c>
     </row>
@@ -1652,19 +1657,19 @@
       <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="6">
         <v>35680</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="6">
         <v>40241.173000000003</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="6">
         <v>36860.444000000003</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="6">
         <v>35395.089</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="6">
         <v>37309.811999999998</v>
       </c>
     </row>
@@ -1672,19 +1677,19 @@
       <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="6">
         <v>400</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="6">
         <v>400</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="6">
         <v>400</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="6">
         <v>220</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="6">
         <v>245</v>
       </c>
     </row>
@@ -1692,19 +1697,19 @@
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="6">
         <v>1408</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="6">
         <v>1498</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="6">
         <v>1543</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="6">
         <v>1181</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="6">
         <v>1336</v>
       </c>
     </row>
@@ -1712,19 +1717,19 @@
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="6">
         <v>242.59800000000001</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="6">
         <v>306.892</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="6">
         <v>271.05700000000002</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="6">
         <v>241.31</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="6">
         <v>249.45699999999999</v>
       </c>
     </row>
@@ -1732,19 +1737,19 @@
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="7">
-        <v>0</v>
-      </c>
-      <c r="C47" s="7">
-        <v>0</v>
-      </c>
-      <c r="D47" s="7">
-        <v>0</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0</v>
-      </c>
-      <c r="F47" s="7">
+      <c r="B47" s="6">
+        <v>0</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0</v>
+      </c>
+      <c r="F47" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1752,19 +1757,19 @@
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B48" s="7">
-        <v>0</v>
-      </c>
-      <c r="C48" s="7">
-        <v>0</v>
-      </c>
-      <c r="D48" s="7">
-        <v>0</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7">
+      <c r="B48" s="6">
+        <v>0</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1772,19 +1777,19 @@
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="6">
         <v>1513.1659999999999</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="6">
         <v>1099.75596335</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="6">
         <v>857.22699999999998</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="6">
         <v>477.25665237999999</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="6">
         <v>240</v>
       </c>
     </row>
@@ -1792,19 +1797,19 @@
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="7">
-        <v>0</v>
-      </c>
-      <c r="C50" s="7">
-        <v>0</v>
-      </c>
-      <c r="D50" s="7">
-        <v>0</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0</v>
-      </c>
-      <c r="F50" s="7">
+      <c r="B50" s="6">
+        <v>0</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0</v>
+      </c>
+      <c r="F50" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1812,19 +1817,19 @@
       <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="6">
         <v>100256.47</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="6">
         <v>118201.36</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="6">
         <v>125377.231</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="6">
         <v>140760.73000000001</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="6">
         <v>149420.9</v>
       </c>
     </row>
@@ -1832,19 +1837,19 @@
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="6">
         <v>12871.370999999999</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="6">
         <v>14834.811</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="6">
         <v>15567.858</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="6">
         <v>16845.719000000001</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="6">
         <v>18642.174999999999</v>
       </c>
     </row>
@@ -1852,19 +1857,19 @@
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="6">
         <v>28990.09</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="6">
         <v>28320</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="6">
         <v>30593</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="6">
         <v>30698</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="6">
         <v>31357</v>
       </c>
     </row>
@@ -1872,19 +1877,19 @@
       <c r="A54" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="6">
         <v>1980</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="6">
         <v>2750</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="6">
         <v>3300</v>
       </c>
-      <c r="E54" s="7">
+      <c r="E54" s="6">
         <v>2755</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54" s="6">
         <v>3020</v>
       </c>
     </row>
@@ -1892,19 +1897,19 @@
       <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B55" s="7">
-        <v>0</v>
-      </c>
-      <c r="C55" s="7">
-        <v>0</v>
-      </c>
-      <c r="D55" s="7">
-        <v>0</v>
-      </c>
-      <c r="E55" s="7">
-        <v>0</v>
-      </c>
-      <c r="F55" s="7">
+      <c r="B55" s="6">
+        <v>0</v>
+      </c>
+      <c r="C55" s="6">
+        <v>0</v>
+      </c>
+      <c r="D55" s="6">
+        <v>0</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0</v>
+      </c>
+      <c r="F55" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1912,19 +1917,19 @@
       <c r="A56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="6">
         <v>300</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="6">
         <v>300</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="6">
         <v>300</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="6">
         <v>300</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="6">
         <v>300</v>
       </c>
     </row>
@@ -1932,19 +1937,19 @@
       <c r="A57" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="6">
         <v>20379.131000000001</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C57" s="6">
         <v>24412.743999999999</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="6">
         <v>21598.148000000001</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="6">
         <v>21055.848999999998</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57" s="6">
         <v>20007.008999999998</v>
       </c>
     </row>
@@ -1952,19 +1957,19 @@
       <c r="A58" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="7">
-        <v>0</v>
-      </c>
-      <c r="C58" s="7">
-        <v>0</v>
-      </c>
-      <c r="D58" s="7">
-        <v>0</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0</v>
-      </c>
-      <c r="F58" s="7">
+      <c r="B58" s="6">
+        <v>0</v>
+      </c>
+      <c r="C58" s="6">
+        <v>0</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0</v>
+      </c>
+      <c r="F58" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1972,19 +1977,19 @@
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="7">
-        <v>0</v>
-      </c>
-      <c r="C59" s="7">
-        <v>0</v>
-      </c>
-      <c r="D59" s="7">
-        <v>0</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0</v>
-      </c>
-      <c r="F59" s="7">
+      <c r="B59" s="6">
+        <v>0</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0</v>
+      </c>
+      <c r="F59" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1992,19 +1997,19 @@
       <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="6">
         <v>83186.485000000001</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="6">
         <v>96336.009000000005</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="6">
         <v>89226.801000000007</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E60" s="6">
         <v>87000.793000000005</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60" s="6">
         <v>84008.865999999995</v>
       </c>
     </row>
@@ -2012,19 +2017,19 @@
       <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="6">
         <v>350</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="6">
         <v>350</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="6">
         <v>350</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="6">
         <v>300</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F61" s="6">
         <v>300</v>
       </c>
     </row>
@@ -2032,19 +2037,19 @@
       <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="6">
         <v>3892.002</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="6">
         <v>4498.9949999999999</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="6">
         <v>4149.5870000000004</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="6">
         <v>3923.3029999999999</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F62" s="6">
         <v>4177.8990000000003</v>
       </c>
     </row>
@@ -2052,19 +2057,19 @@
       <c r="A63" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="6">
         <v>385</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="6">
         <v>485</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="6">
         <v>450</v>
       </c>
-      <c r="E63" s="7">
+      <c r="E63" s="6">
         <v>1365</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F63" s="6">
         <v>1750</v>
       </c>
     </row>
@@ -2072,19 +2077,19 @@
       <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="6">
         <v>1300</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="6">
         <v>1300</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D64" s="6">
         <v>900</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E64" s="6">
         <v>1000</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64" s="6">
         <v>1014</v>
       </c>
     </row>
@@ -2092,19 +2097,19 @@
       <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B65" s="7">
-        <v>0</v>
-      </c>
-      <c r="C65" s="7">
-        <v>0</v>
-      </c>
-      <c r="D65" s="7">
-        <v>0</v>
-      </c>
-      <c r="E65" s="7">
-        <v>0</v>
-      </c>
-      <c r="F65" s="7">
+      <c r="B65" s="6">
+        <v>0</v>
+      </c>
+      <c r="C65" s="6">
+        <v>0</v>
+      </c>
+      <c r="D65" s="6">
+        <v>0</v>
+      </c>
+      <c r="E65" s="6">
+        <v>0</v>
+      </c>
+      <c r="F65" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2112,19 +2117,19 @@
       <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B66" s="7">
-        <v>0</v>
-      </c>
-      <c r="C66" s="7">
-        <v>0</v>
-      </c>
-      <c r="D66" s="7">
-        <v>0</v>
-      </c>
-      <c r="E66" s="7">
-        <v>0</v>
-      </c>
-      <c r="F66" s="7">
+      <c r="B66" s="6">
+        <v>0</v>
+      </c>
+      <c r="C66" s="6">
+        <v>0</v>
+      </c>
+      <c r="D66" s="6">
+        <v>0</v>
+      </c>
+      <c r="E66" s="6">
+        <v>0</v>
+      </c>
+      <c r="F66" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2132,19 +2137,19 @@
       <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B67" s="7">
-        <v>0</v>
-      </c>
-      <c r="C67" s="7">
-        <v>0</v>
-      </c>
-      <c r="D67" s="7">
-        <v>0</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0</v>
-      </c>
-      <c r="F67" s="7">
+      <c r="B67" s="6">
+        <v>0</v>
+      </c>
+      <c r="C67" s="6">
+        <v>0</v>
+      </c>
+      <c r="D67" s="6">
+        <v>0</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0</v>
+      </c>
+      <c r="F67" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2152,19 +2157,19 @@
       <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="6">
         <v>494.89</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="6">
         <v>651.72500000000002</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="6">
         <v>687.79300000000001</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E68" s="6">
         <v>902.24199999999996</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68" s="6">
         <v>871.92399999999998</v>
       </c>
     </row>
@@ -2172,19 +2177,19 @@
       <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B69" s="7">
-        <v>0</v>
-      </c>
-      <c r="C69" s="7">
-        <v>0</v>
-      </c>
-      <c r="D69" s="7">
-        <v>0</v>
-      </c>
-      <c r="E69" s="7">
-        <v>0</v>
-      </c>
-      <c r="F69" s="7">
+      <c r="B69" s="6">
+        <v>0</v>
+      </c>
+      <c r="C69" s="6">
+        <v>0</v>
+      </c>
+      <c r="D69" s="6">
+        <v>0</v>
+      </c>
+      <c r="E69" s="6">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2192,19 +2197,19 @@
       <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="6">
         <v>1886.403</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="6">
         <v>2073.0680000000002</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="6">
         <v>1874.7919999999999</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E70" s="6">
         <v>1899.54</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="6">
         <v>1824.9770000000001</v>
       </c>
     </row>
@@ -2212,19 +2217,19 @@
       <c r="A71" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="6">
         <v>179.88399999999999</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="6">
         <v>315.43700000000001</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="6">
         <v>248</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E71" s="6">
         <v>295.916</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="6">
         <v>305.00900000000001</v>
       </c>
     </row>
@@ -2232,19 +2237,19 @@
       <c r="A72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="6">
         <v>6618.5439999999999</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="6">
         <v>6739.11</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="6">
         <v>7206.61</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E72" s="6">
         <v>7529.7870000000003</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72" s="6">
         <v>9014.1440000000002</v>
       </c>
     </row>
@@ -2252,19 +2257,19 @@
       <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B73" s="7">
-        <v>0</v>
-      </c>
-      <c r="C73" s="7">
-        <v>0</v>
-      </c>
-      <c r="D73" s="7">
-        <v>0</v>
-      </c>
-      <c r="E73" s="7">
-        <v>0</v>
-      </c>
-      <c r="F73" s="7">
+      <c r="B73" s="6">
+        <v>0</v>
+      </c>
+      <c r="C73" s="6">
+        <v>0</v>
+      </c>
+      <c r="D73" s="6">
+        <v>0</v>
+      </c>
+      <c r="E73" s="6">
+        <v>0</v>
+      </c>
+      <c r="F73" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2272,19 +2277,19 @@
       <c r="A74" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="6">
         <v>16802.559000000001</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C74" s="6">
         <v>18453.593000000001</v>
       </c>
-      <c r="D74" s="7">
+      <c r="D74" s="6">
         <v>18386.331999999999</v>
       </c>
-      <c r="E74" s="7">
+      <c r="E74" s="6">
         <v>16422.52682368</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F74" s="6">
         <v>14325.227999999999</v>
       </c>
     </row>
@@ -2292,19 +2297,19 @@
       <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="6">
         <v>465</v>
       </c>
-      <c r="C75" s="7">
+      <c r="C75" s="6">
         <v>570</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="6">
         <v>560</v>
       </c>
-      <c r="E75" s="7">
+      <c r="E75" s="6">
         <v>500</v>
       </c>
-      <c r="F75" s="7">
+      <c r="F75" s="6">
         <v>400</v>
       </c>
     </row>
@@ -2312,19 +2317,19 @@
       <c r="A76" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="6">
         <v>19.364000000000001</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C76" s="6">
         <v>3.0419999999999998</v>
       </c>
-      <c r="D76" s="7">
-        <v>0</v>
-      </c>
-      <c r="E76" s="7">
-        <v>0</v>
-      </c>
-      <c r="F76" s="7">
+      <c r="D76" s="6">
+        <v>0</v>
+      </c>
+      <c r="E76" s="6">
+        <v>0</v>
+      </c>
+      <c r="F76" s="6">
         <v>5</v>
       </c>
     </row>
@@ -2332,19 +2337,19 @@
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="6">
         <v>1000</v>
       </c>
-      <c r="C77" s="7">
+      <c r="C77" s="6">
         <v>1050</v>
       </c>
-      <c r="D77" s="7">
+      <c r="D77" s="6">
         <v>1550</v>
       </c>
-      <c r="E77" s="7">
+      <c r="E77" s="6">
         <v>1397</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77" s="6">
         <v>1415</v>
       </c>
     </row>
@@ -2352,19 +2357,19 @@
       <c r="A78" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="6">
         <v>350</v>
       </c>
-      <c r="C78" s="7">
+      <c r="C78" s="6">
         <v>400</v>
       </c>
-      <c r="D78" s="7">
+      <c r="D78" s="6">
         <v>400</v>
       </c>
-      <c r="E78" s="7">
+      <c r="E78" s="6">
         <v>500</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F78" s="6">
         <v>500</v>
       </c>
     </row>
@@ -2372,19 +2377,19 @@
       <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="6">
         <v>6053.7259999999997</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C79" s="6">
         <v>6620.4</v>
       </c>
-      <c r="D79" s="7">
+      <c r="D79" s="6">
         <v>6142.9690000000001</v>
       </c>
-      <c r="E79" s="7">
+      <c r="E79" s="6">
         <v>4676.8389999999999</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79" s="6">
         <v>6395.45</v>
       </c>
     </row>
@@ -2392,19 +2397,19 @@
       <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="6">
         <v>585.65</v>
       </c>
-      <c r="C80" s="7">
+      <c r="C80" s="6">
         <v>645.654</v>
       </c>
-      <c r="D80" s="7">
+      <c r="D80" s="6">
         <v>569.93399999999997</v>
       </c>
-      <c r="E80" s="7">
+      <c r="E80" s="6">
         <v>554.53899999999999</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80" s="6">
         <v>566.029</v>
       </c>
     </row>
@@ -2412,19 +2417,19 @@
       <c r="A81" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="7">
-        <v>0</v>
-      </c>
-      <c r="C81" s="7">
-        <v>0</v>
-      </c>
-      <c r="D81" s="7">
-        <v>0</v>
-      </c>
-      <c r="E81" s="7">
-        <v>0</v>
-      </c>
-      <c r="F81" s="7">
+      <c r="B81" s="6">
+        <v>0</v>
+      </c>
+      <c r="C81" s="6">
+        <v>0</v>
+      </c>
+      <c r="D81" s="6">
+        <v>0</v>
+      </c>
+      <c r="E81" s="6">
+        <v>0</v>
+      </c>
+      <c r="F81" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2432,19 +2437,19 @@
       <c r="A82" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B82" s="7">
+      <c r="B82" s="6">
         <v>650</v>
       </c>
-      <c r="C82" s="7">
+      <c r="C82" s="6">
         <v>650</v>
       </c>
-      <c r="D82" s="7">
+      <c r="D82" s="6">
         <v>650</v>
       </c>
-      <c r="E82" s="7">
+      <c r="E82" s="6">
         <v>1190</v>
       </c>
-      <c r="F82" s="7">
+      <c r="F82" s="6">
         <v>1200</v>
       </c>
     </row>
@@ -2452,19 +2457,19 @@
       <c r="A83" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B83" s="7">
+      <c r="B83" s="6">
         <v>623.84</v>
       </c>
-      <c r="C83" s="7">
+      <c r="C83" s="6">
         <v>622.48199999999997</v>
       </c>
-      <c r="D83" s="7">
+      <c r="D83" s="6">
         <v>703.923</v>
       </c>
-      <c r="E83" s="7">
+      <c r="E83" s="6">
         <v>689.88400000000001</v>
       </c>
-      <c r="F83" s="7">
+      <c r="F83" s="6">
         <v>610.10599999999999</v>
       </c>
     </row>
@@ -2472,19 +2477,19 @@
       <c r="A84" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="6">
         <v>2500</v>
       </c>
-      <c r="C84" s="7">
+      <c r="C84" s="6">
         <v>2800</v>
       </c>
-      <c r="D84" s="7">
+      <c r="D84" s="6">
         <v>2900</v>
       </c>
-      <c r="E84" s="7">
+      <c r="E84" s="6">
         <v>2900</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F84" s="6">
         <v>3030</v>
       </c>
     </row>
@@ -2492,19 +2497,19 @@
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B85" s="7">
+      <c r="B85" s="6">
         <v>315</v>
       </c>
-      <c r="C85" s="7">
+      <c r="C85" s="6">
         <v>320.92599999999999</v>
       </c>
-      <c r="D85" s="7">
+      <c r="D85" s="6">
         <v>319.97266999999999</v>
       </c>
-      <c r="E85" s="7">
+      <c r="E85" s="6">
         <v>1412.6804999999999</v>
       </c>
-      <c r="F85" s="7">
+      <c r="F85" s="6">
         <v>2290.9870999999998</v>
       </c>
     </row>
@@ -2512,19 +2517,19 @@
       <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="6">
         <v>3803</v>
       </c>
-      <c r="C86" s="7">
+      <c r="C86" s="6">
         <v>5437.6660000000002</v>
       </c>
-      <c r="D86" s="7">
+      <c r="D86" s="6">
         <v>6013</v>
       </c>
-      <c r="E86" s="7">
+      <c r="E86" s="6">
         <v>5337</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F86" s="6">
         <v>4127</v>
       </c>
     </row>
@@ -2532,19 +2537,19 @@
       <c r="A87" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="7">
-        <v>0</v>
-      </c>
-      <c r="C87" s="7">
-        <v>0</v>
-      </c>
-      <c r="D87" s="7">
-        <v>0</v>
-      </c>
-      <c r="E87" s="7">
-        <v>0</v>
-      </c>
-      <c r="F87" s="7">
+      <c r="B87" s="6">
+        <v>0</v>
+      </c>
+      <c r="C87" s="6">
+        <v>0</v>
+      </c>
+      <c r="D87" s="6">
+        <v>0</v>
+      </c>
+      <c r="E87" s="6">
+        <v>0</v>
+      </c>
+      <c r="F87" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2552,19 +2557,19 @@
       <c r="A88" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="6">
         <v>23.283999999999999</v>
       </c>
-      <c r="C88" s="7">
+      <c r="C88" s="6">
         <v>26.492999999999999</v>
       </c>
-      <c r="D88" s="7">
+      <c r="D88" s="6">
         <v>23.619</v>
       </c>
-      <c r="E88" s="7">
+      <c r="E88" s="6">
         <v>21.157</v>
       </c>
-      <c r="F88" s="7">
+      <c r="F88" s="6">
         <v>21.943000000000001</v>
       </c>
     </row>
@@ -2572,19 +2577,19 @@
       <c r="A89" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89" s="6">
         <v>730.68</v>
       </c>
-      <c r="C89" s="7">
+      <c r="C89" s="6">
         <v>1234.0989999999999</v>
       </c>
-      <c r="D89" s="7">
+      <c r="D89" s="6">
         <v>1765.154</v>
       </c>
-      <c r="E89" s="7">
+      <c r="E89" s="6">
         <v>1558.8589999999999</v>
       </c>
-      <c r="F89" s="7">
+      <c r="F89" s="6">
         <v>1526.819</v>
       </c>
     </row>
@@ -2592,19 +2597,19 @@
       <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="6">
         <v>892.31100000000004</v>
       </c>
-      <c r="C90" s="7">
+      <c r="C90" s="6">
         <v>1554.825</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="6">
         <v>1600</v>
       </c>
-      <c r="E90" s="7">
+      <c r="E90" s="6">
         <v>1851</v>
       </c>
-      <c r="F90" s="7">
+      <c r="F90" s="6">
         <v>1829.54</v>
       </c>
     </row>
@@ -2612,19 +2617,19 @@
       <c r="A91" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="6">
         <v>7855.8630000000003</v>
       </c>
-      <c r="C91" s="7">
+      <c r="C91" s="6">
         <v>8454.107</v>
       </c>
-      <c r="D91" s="7">
+      <c r="D91" s="6">
         <v>7407.0770000000002</v>
       </c>
-      <c r="E91" s="7">
+      <c r="E91" s="6">
         <v>6427.7759999999998</v>
       </c>
-      <c r="F91" s="7">
+      <c r="F91" s="6">
         <v>7112.808</v>
       </c>
     </row>
@@ -2632,19 +2637,19 @@
       <c r="A92" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="6">
         <v>2202.77</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="6">
         <v>1952.971</v>
       </c>
-      <c r="D92" s="7">
+      <c r="D92" s="6">
         <v>1854.867</v>
       </c>
-      <c r="E92" s="7">
+      <c r="E92" s="6">
         <v>2039.6559999999999</v>
       </c>
-      <c r="F92" s="7">
+      <c r="F92" s="6">
         <v>1948.3320000000001</v>
       </c>
     </row>
@@ -2652,19 +2657,19 @@
       <c r="A93" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="6">
         <v>1218.0730000000001</v>
       </c>
-      <c r="C93" s="7">
+      <c r="C93" s="6">
         <v>1001.799</v>
       </c>
-      <c r="D93" s="7">
+      <c r="D93" s="6">
         <v>1081.914</v>
       </c>
-      <c r="E93" s="7">
+      <c r="E93" s="6">
         <v>1146.4364700000001</v>
       </c>
-      <c r="F93" s="7">
+      <c r="F93" s="6">
         <v>1176.548</v>
       </c>
     </row>
@@ -2672,19 +2677,19 @@
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="6">
         <v>2790.433</v>
       </c>
-      <c r="C94" s="7">
+      <c r="C94" s="6">
         <v>3375.4380000000001</v>
       </c>
-      <c r="D94" s="7">
+      <c r="D94" s="6">
         <v>2625.2620000000002</v>
       </c>
-      <c r="E94" s="7">
+      <c r="E94" s="6">
         <v>1621.5519999999999</v>
       </c>
-      <c r="F94" s="7">
+      <c r="F94" s="6">
         <v>1364.279</v>
       </c>
     </row>
@@ -2692,19 +2697,19 @@
       <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="6">
         <v>71620.960000000006</v>
       </c>
-      <c r="C95" s="7">
+      <c r="C95" s="6">
         <v>77019.856</v>
       </c>
-      <c r="D95" s="7">
+      <c r="D95" s="6">
         <v>71469.183000000005</v>
       </c>
-      <c r="E95" s="7">
+      <c r="E95" s="6">
         <v>76028.645000000004</v>
       </c>
-      <c r="F95" s="7">
+      <c r="F95" s="6">
         <v>71006.917000000001</v>
       </c>
     </row>
@@ -2712,19 +2717,19 @@
       <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="6">
         <v>7775</v>
       </c>
-      <c r="C96" s="7">
+      <c r="C96" s="6">
         <v>8735</v>
       </c>
-      <c r="D96" s="7">
+      <c r="D96" s="6">
         <v>9860.1990000000005</v>
       </c>
-      <c r="E96" s="7">
+      <c r="E96" s="6">
         <v>9940.3629999999994</v>
       </c>
-      <c r="F96" s="7">
+      <c r="F96" s="6">
         <v>9605.7189999999991</v>
       </c>
     </row>
@@ -2732,19 +2737,19 @@
       <c r="A97" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B97" s="7">
-        <v>0</v>
-      </c>
-      <c r="C97" s="7">
-        <v>0</v>
-      </c>
-      <c r="D97" s="7">
-        <v>0</v>
-      </c>
-      <c r="E97" s="7">
-        <v>0</v>
-      </c>
-      <c r="F97" s="7">
+      <c r="B97" s="6">
+        <v>0</v>
+      </c>
+      <c r="C97" s="6">
+        <v>0</v>
+      </c>
+      <c r="D97" s="6">
+        <v>0</v>
+      </c>
+      <c r="E97" s="6">
+        <v>0</v>
+      </c>
+      <c r="F97" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2752,19 +2757,19 @@
       <c r="A98" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="6">
         <v>1455.7</v>
       </c>
-      <c r="C98" s="7">
+      <c r="C98" s="6">
         <v>1667.4</v>
       </c>
-      <c r="D98" s="7">
+      <c r="D98" s="6">
         <v>1674.1</v>
       </c>
-      <c r="E98" s="7">
+      <c r="E98" s="6">
         <v>1454</v>
       </c>
-      <c r="F98" s="7">
+      <c r="F98" s="6">
         <v>1393.2</v>
       </c>
     </row>
@@ -2772,19 +2777,19 @@
       <c r="A99" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B99" s="7">
-        <v>0</v>
-      </c>
-      <c r="C99" s="7">
-        <v>0</v>
-      </c>
-      <c r="D99" s="7">
-        <v>0</v>
-      </c>
-      <c r="E99" s="7">
-        <v>0</v>
-      </c>
-      <c r="F99" s="7">
+      <c r="B99" s="6">
+        <v>0</v>
+      </c>
+      <c r="C99" s="6">
+        <v>0</v>
+      </c>
+      <c r="D99" s="6">
+        <v>0</v>
+      </c>
+      <c r="E99" s="6">
+        <v>0</v>
+      </c>
+      <c r="F99" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2792,19 +2797,19 @@
       <c r="A100" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="6">
         <v>419.45499999999998</v>
       </c>
-      <c r="C100" s="7">
+      <c r="C100" s="6">
         <v>567.94000000000005</v>
       </c>
-      <c r="D100" s="7">
+      <c r="D100" s="6">
         <v>547.51</v>
       </c>
-      <c r="E100" s="7">
+      <c r="E100" s="6">
         <v>465.18700000000001</v>
       </c>
-      <c r="F100" s="7">
+      <c r="F100" s="6">
         <v>259.495</v>
       </c>
     </row>
@@ -2812,19 +2817,19 @@
       <c r="A101" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="6">
         <v>3443.5149999999999</v>
       </c>
-      <c r="C101" s="7">
+      <c r="C101" s="6">
         <v>4862.8389999999999</v>
       </c>
-      <c r="D101" s="7">
+      <c r="D101" s="6">
         <v>3872.23</v>
       </c>
-      <c r="E101" s="7">
+      <c r="E101" s="6">
         <v>4376.9369999999999</v>
       </c>
-      <c r="F101" s="7">
+      <c r="F101" s="6">
         <v>3865.7939999999999</v>
       </c>
     </row>
@@ -2832,19 +2837,19 @@
       <c r="A102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="6">
         <v>585.19799999999998</v>
       </c>
-      <c r="C102" s="7">
+      <c r="C102" s="6">
         <v>661.91499999999996</v>
       </c>
-      <c r="D102" s="7">
+      <c r="D102" s="6">
         <v>601.25599999999997</v>
       </c>
-      <c r="E102" s="7">
+      <c r="E102" s="6">
         <v>526.06700000000001</v>
       </c>
-      <c r="F102" s="7">
+      <c r="F102" s="6">
         <v>594.61099999999999</v>
       </c>
     </row>
@@ -2852,19 +2857,19 @@
       <c r="A103" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="6">
         <v>3876.5</v>
       </c>
-      <c r="C103" s="7">
+      <c r="C103" s="6">
         <v>5019.5</v>
       </c>
-      <c r="D103" s="7">
+      <c r="D103" s="6">
         <v>4495.6099999999997</v>
       </c>
-      <c r="E103" s="7">
+      <c r="E103" s="6">
         <v>4953.0600000000004</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F103" s="6">
         <v>4716.91</v>
       </c>
     </row>
@@ -2872,19 +2877,19 @@
       <c r="A104" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="6">
         <v>67078.762000000002</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="6">
         <v>70418.035999999993</v>
       </c>
-      <c r="D104" s="7">
+      <c r="D104" s="6">
         <v>65846.167000000001</v>
       </c>
-      <c r="E104" s="7">
+      <c r="E104" s="6">
         <v>66683.28</v>
       </c>
-      <c r="F104" s="7">
+      <c r="F104" s="6">
         <v>63648.377</v>
       </c>
     </row>
@@ -2892,19 +2897,19 @@
       <c r="A105" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="6">
         <v>10998.424000000001</v>
       </c>
-      <c r="C105" s="7">
+      <c r="C105" s="6">
         <v>14204.897999999999</v>
       </c>
-      <c r="D105" s="7">
+      <c r="D105" s="6">
         <v>11573.09</v>
       </c>
-      <c r="E105" s="7">
+      <c r="E105" s="6">
         <v>11445.439</v>
       </c>
-      <c r="F105" s="7">
+      <c r="F105" s="6">
         <v>11872.543</v>
       </c>
     </row>
@@ -2912,19 +2917,19 @@
       <c r="A106" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="6">
         <v>30</v>
       </c>
-      <c r="C106" s="7">
+      <c r="C106" s="6">
         <v>30</v>
       </c>
-      <c r="D106" s="7">
+      <c r="D106" s="6">
         <v>30</v>
       </c>
-      <c r="E106" s="7">
+      <c r="E106" s="6">
         <v>30</v>
       </c>
-      <c r="F106" s="7">
+      <c r="F106" s="6">
         <v>30</v>
       </c>
     </row>
@@ -2932,19 +2937,19 @@
       <c r="A107" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B107" s="7">
-        <v>0</v>
-      </c>
-      <c r="C107" s="7">
-        <v>0</v>
-      </c>
-      <c r="D107" s="7">
-        <v>0</v>
-      </c>
-      <c r="E107" s="7">
-        <v>0</v>
-      </c>
-      <c r="F107" s="7">
+      <c r="B107" s="6">
+        <v>0</v>
+      </c>
+      <c r="C107" s="6">
+        <v>0</v>
+      </c>
+      <c r="D107" s="6">
+        <v>0</v>
+      </c>
+      <c r="E107" s="6">
+        <v>0</v>
+      </c>
+      <c r="F107" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2952,19 +2957,19 @@
       <c r="A108" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="6">
         <v>4408.6509999999998</v>
       </c>
-      <c r="C108" s="7">
+      <c r="C108" s="6">
         <v>4678.2870000000003</v>
       </c>
-      <c r="D108" s="7">
+      <c r="D108" s="6">
         <v>4404.1959999999999</v>
       </c>
-      <c r="E108" s="7">
+      <c r="E108" s="6">
         <v>4258.3810000000003</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F108" s="6">
         <v>4024.7950000000001</v>
       </c>
     </row>
@@ -2972,19 +2977,19 @@
       <c r="A109" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="6">
         <v>1175</v>
       </c>
-      <c r="C109" s="7">
+      <c r="C109" s="6">
         <v>1291.0999999999999</v>
       </c>
-      <c r="D109" s="7">
+      <c r="D109" s="6">
         <v>1205.9000000000001</v>
       </c>
-      <c r="E109" s="7">
+      <c r="E109" s="6">
         <v>1200</v>
       </c>
-      <c r="F109" s="7">
+      <c r="F109" s="6">
         <v>1200</v>
       </c>
     </row>
@@ -2992,19 +2997,19 @@
       <c r="A110" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="6">
         <v>5</v>
       </c>
-      <c r="C110" s="7">
+      <c r="C110" s="6">
         <v>5</v>
       </c>
-      <c r="D110" s="7">
-        <v>0</v>
-      </c>
-      <c r="E110" s="7">
-        <v>0</v>
-      </c>
-      <c r="F110" s="7">
+      <c r="D110" s="6">
+        <v>0</v>
+      </c>
+      <c r="E110" s="6">
+        <v>0</v>
+      </c>
+      <c r="F110" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3012,19 +3017,19 @@
       <c r="A111" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="6">
         <v>20958.917000000001</v>
       </c>
-      <c r="C111" s="7">
+      <c r="C111" s="6">
         <v>23233.300999999999</v>
       </c>
-      <c r="D111" s="7">
+      <c r="D111" s="6">
         <v>20801.198</v>
       </c>
-      <c r="E111" s="7">
+      <c r="E111" s="6">
         <v>19149.178</v>
       </c>
-      <c r="F111" s="7">
+      <c r="F111" s="6">
         <v>19195.303</v>
       </c>
     </row>
@@ -3032,19 +3037,19 @@
       <c r="A112" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B112" s="7">
-        <v>0</v>
-      </c>
-      <c r="C112" s="7">
-        <v>0</v>
-      </c>
-      <c r="D112" s="7">
-        <v>0</v>
-      </c>
-      <c r="E112" s="7">
-        <v>0</v>
-      </c>
-      <c r="F112" s="7">
+      <c r="B112" s="6">
+        <v>0</v>
+      </c>
+      <c r="C112" s="6">
+        <v>0</v>
+      </c>
+      <c r="D112" s="6">
+        <v>0</v>
+      </c>
+      <c r="E112" s="6">
+        <v>0</v>
+      </c>
+      <c r="F112" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3052,19 +3057,19 @@
       <c r="A113" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="6">
         <v>120</v>
       </c>
-      <c r="C113" s="7">
+      <c r="C113" s="6">
         <v>145</v>
       </c>
-      <c r="D113" s="7">
+      <c r="D113" s="6">
         <v>140</v>
       </c>
-      <c r="E113" s="7">
+      <c r="E113" s="6">
         <v>695</v>
       </c>
-      <c r="F113" s="7">
+      <c r="F113" s="6">
         <v>750</v>
       </c>
     </row>
@@ -3072,19 +3077,19 @@
       <c r="A114" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="6">
         <v>4467.2190000000001</v>
       </c>
-      <c r="C114" s="7">
+      <c r="C114" s="6">
         <v>5472.9260000000004</v>
       </c>
-      <c r="D114" s="7">
+      <c r="D114" s="6">
         <v>5316.44</v>
       </c>
-      <c r="E114" s="7">
+      <c r="E114" s="6">
         <v>4976.2619999999997</v>
       </c>
-      <c r="F114" s="7">
+      <c r="F114" s="6">
         <v>4918.4459999999999</v>
       </c>
     </row>
@@ -3092,19 +3097,19 @@
       <c r="A115" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B115" s="7">
-        <v>0</v>
-      </c>
-      <c r="C115" s="7">
-        <v>0</v>
-      </c>
-      <c r="D115" s="7">
-        <v>0</v>
-      </c>
-      <c r="E115" s="7">
-        <v>0</v>
-      </c>
-      <c r="F115" s="7">
+      <c r="B115" s="6">
+        <v>0</v>
+      </c>
+      <c r="C115" s="6">
+        <v>0</v>
+      </c>
+      <c r="D115" s="6">
+        <v>0</v>
+      </c>
+      <c r="E115" s="6">
+        <v>0</v>
+      </c>
+      <c r="F115" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3112,19 +3117,19 @@
       <c r="A116" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="6">
         <v>77.599999999999994</v>
       </c>
-      <c r="C116" s="7">
+      <c r="C116" s="6">
         <v>85.1</v>
       </c>
-      <c r="D116" s="7">
+      <c r="D116" s="6">
         <v>80</v>
       </c>
-      <c r="E116" s="7">
+      <c r="E116" s="6">
         <v>84</v>
       </c>
-      <c r="F116" s="7">
+      <c r="F116" s="6">
         <v>73</v>
       </c>
     </row>
@@ -3132,19 +3137,19 @@
       <c r="A117" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B117" s="7">
-        <v>0</v>
-      </c>
-      <c r="C117" s="7">
-        <v>0</v>
-      </c>
-      <c r="D117" s="7">
-        <v>0</v>
-      </c>
-      <c r="E117" s="7">
-        <v>0</v>
-      </c>
-      <c r="F117" s="7">
+      <c r="B117" s="6">
+        <v>0</v>
+      </c>
+      <c r="C117" s="6">
+        <v>0</v>
+      </c>
+      <c r="D117" s="6">
+        <v>0</v>
+      </c>
+      <c r="E117" s="6">
+        <v>0</v>
+      </c>
+      <c r="F117" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3152,19 +3157,19 @@
       <c r="A118" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="6">
         <v>35810.250999999997</v>
       </c>
-      <c r="C118" s="7">
+      <c r="C118" s="6">
         <v>40360.044999999998</v>
       </c>
-      <c r="D118" s="7">
+      <c r="D118" s="6">
         <v>35133.777999999998</v>
       </c>
-      <c r="E118" s="7">
+      <c r="E118" s="6">
         <v>33713.680999999997</v>
       </c>
-      <c r="F118" s="7">
+      <c r="F118" s="6">
         <v>36893.392</v>
       </c>
     </row>
@@ -3172,19 +3177,19 @@
       <c r="A119" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="6">
         <v>20616.368999999999</v>
       </c>
-      <c r="C119" s="7">
+      <c r="C119" s="6">
         <v>21365.563999999998</v>
       </c>
-      <c r="D119" s="7">
+      <c r="D119" s="6">
         <v>6263.232</v>
       </c>
-      <c r="E119" s="7">
+      <c r="E119" s="6">
         <v>6227.7</v>
       </c>
-      <c r="F119" s="7">
+      <c r="F119" s="6">
         <v>7575.2</v>
       </c>
     </row>
@@ -3192,19 +3197,19 @@
       <c r="A120" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="6">
         <v>2721.9879999999998</v>
       </c>
-      <c r="C120" s="7">
+      <c r="C120" s="6">
         <v>2997.46</v>
       </c>
-      <c r="D120" s="7">
+      <c r="D120" s="6">
         <v>3696.451</v>
       </c>
-      <c r="E120" s="7">
+      <c r="E120" s="6">
         <v>3772.5410000000002</v>
       </c>
-      <c r="F120" s="7">
+      <c r="F120" s="6">
         <v>3725</v>
       </c>
     </row>
@@ -3212,19 +3217,19 @@
       <c r="A121" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="6">
         <v>7085.7470000000003</v>
       </c>
-      <c r="C121" s="7">
+      <c r="C121" s="6">
         <v>7221.59</v>
       </c>
-      <c r="D121" s="7">
+      <c r="D121" s="6">
         <v>5962.7979999999998</v>
       </c>
-      <c r="E121" s="7">
+      <c r="E121" s="6">
         <v>5616.5360000000001</v>
       </c>
-      <c r="F121" s="7">
+      <c r="F121" s="6">
         <v>4011.9404</v>
       </c>
     </row>
@@ -3232,19 +3237,19 @@
       <c r="A122" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="6">
         <v>72732.127999999997</v>
       </c>
-      <c r="C122" s="7">
+      <c r="C122" s="6">
         <v>85791.41</v>
       </c>
-      <c r="D122" s="7">
+      <c r="D122" s="6">
         <v>80535.396999999997</v>
       </c>
-      <c r="E122" s="7">
+      <c r="E122" s="6">
         <v>81392.248999999996</v>
       </c>
-      <c r="F122" s="7">
+      <c r="F122" s="6">
         <v>79456.591</v>
       </c>
     </row>
@@ -3252,19 +3257,19 @@
       <c r="A123" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="6">
         <v>49.088999999999999</v>
       </c>
-      <c r="C123" s="7">
+      <c r="C123" s="6">
         <v>62.75</v>
       </c>
-      <c r="D123" s="7">
+      <c r="D123" s="6">
         <v>54.869</v>
       </c>
-      <c r="E123" s="7">
+      <c r="E123" s="6">
         <v>48.331000000000003</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F123" s="6">
         <v>50.228000000000002</v>
       </c>
     </row>
@@ -3272,19 +3277,19 @@
       <c r="A124" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="6">
         <v>939.19799999999998</v>
       </c>
-      <c r="C124" s="7">
+      <c r="C124" s="6">
         <v>1050</v>
       </c>
-      <c r="D124" s="7">
+      <c r="D124" s="6">
         <v>950</v>
       </c>
-      <c r="E124" s="7">
+      <c r="E124" s="6">
         <v>1000</v>
       </c>
-      <c r="F124" s="7">
+      <c r="F124" s="6">
         <v>1000</v>
       </c>
     </row>
@@ -3292,19 +3297,19 @@
       <c r="A125" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="6">
         <v>29.152999999999999</v>
       </c>
-      <c r="C125" s="7">
+      <c r="C125" s="6">
         <v>29.427</v>
       </c>
-      <c r="D125" s="7">
+      <c r="D125" s="6">
         <v>27.128</v>
       </c>
-      <c r="E125" s="7">
+      <c r="E125" s="6">
         <v>27.388000000000002</v>
       </c>
-      <c r="F125" s="7">
+      <c r="F125" s="6">
         <v>28.748999999999999</v>
       </c>
     </row>
@@ -3312,19 +3317,19 @@
       <c r="A126" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="6">
         <v>19900</v>
       </c>
-      <c r="C126" s="7">
+      <c r="C126" s="6">
         <v>23019</v>
       </c>
-      <c r="D126" s="7">
+      <c r="D126" s="6">
         <v>20003.558000000001</v>
       </c>
-      <c r="E126" s="7">
+      <c r="E126" s="6">
         <v>19214.832999999999</v>
       </c>
-      <c r="F126" s="7">
+      <c r="F126" s="6">
         <v>21974.437999999998</v>
       </c>
     </row>
@@ -3332,19 +3337,19 @@
       <c r="A127" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="6">
         <v>1883323.0830000001</v>
       </c>
-      <c r="C127" s="7">
+      <c r="C127" s="6">
         <v>1962510.2649634001</v>
       </c>
-      <c r="D127" s="7">
+      <c r="D127" s="6">
         <v>1889251.0531200001</v>
       </c>
-      <c r="E127" s="7">
+      <c r="E127" s="6">
         <v>1904119.9904461</v>
       </c>
-      <c r="F127" s="7">
+      <c r="F127" s="6">
         <v>1886929.3875</v>
       </c>
     </row>
@@ -3352,24 +3357,24 @@
       <c r="A128" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="6">
         <v>50</v>
       </c>
-      <c r="C128" s="7">
+      <c r="C128" s="6">
         <v>50</v>
       </c>
-      <c r="D128" s="7">
+      <c r="D128" s="6">
         <v>60</v>
       </c>
-      <c r="E128" s="7">
+      <c r="E128" s="6">
         <v>100</v>
       </c>
-      <c r="F128" s="7">
+      <c r="F128" s="6">
         <v>107</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A129" s="3"/>
+      <c r="A129" s="2"/>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A130" s="8" t="s">
@@ -3406,7 +3411,7 @@
       <c r="N131" s="8"/>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="7" t="s">
         <v>127</v>
       </c>
     </row>
@@ -3414,7 +3419,7 @@
       <c r="A133" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B133" s="4">
+      <c r="B133" s="3">
         <v>46040.638842592591</v>
       </c>
     </row>

--- a/industry/input_data/steel/Worldsteel-totalproductionofcrudesteel.xlsx
+++ b/industry/input_data/steel/Worldsteel-totalproductionofcrudesteel.xlsx
@@ -1,21 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fraunhofer-my.sharepoint.com/personal/rakesh_etikala_narendar_iee_fraunhofer_de/Documents/Desktop/sectoral-energy-demands/industry/input_data/steel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_3352B0E1F3F105F010E720AC36A94142DD0FB1ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA850618-9864-4111-B91A-DAB19A6736F3}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_3352B0E1F3F105F010E720AC36A94142DD0FB1ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D8E9E39-47C6-41DB-8ACC-69454DABC7A9}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="16870" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="22320" windowHeight="17770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P1_crude_steel_total_pub" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">P1_crude_steel_total_pub!$A$3:$F$128</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -837,6 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:N136"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -873,7 +890,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -893,7 +910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -913,7 +930,7 @@
         <v>4520</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,7 +950,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -953,7 +970,7 @@
         <v>3862.6080000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -973,7 +990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -993,7 +1010,7 @@
         <v>4657.826</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1013,7 +1030,7 @@
         <v>7129.8720000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1033,7 +1050,7 @@
         <v>354.82299999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1053,7 +1070,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1073,7 +1090,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -1093,7 +1110,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -1113,7 +1130,7 @@
         <v>7134.81</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1133,7 +1150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1153,7 +1170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -1173,7 +1190,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1193,7 +1210,7 @@
         <v>33880.195</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -1213,7 +1230,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -1233,7 +1250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -1253,7 +1270,7 @@
         <v>12349.087</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -1273,7 +1290,7 @@
         <v>824.154</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -1293,7 +1310,7 @@
         <v>1005090</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -1313,7 +1330,7 @@
         <v>1284.4390000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -1333,7 +1350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -1353,7 +1370,7 @@
         <v>153.249</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -1373,7 +1390,7 @@
         <v>178.69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -1393,7 +1410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -1413,7 +1430,7 @@
         <v>2547.915</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -1433,7 +1450,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -1453,7 +1470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -1473,7 +1490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -1493,7 +1510,7 @@
         <v>492.64400000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -1513,7 +1530,7 @@
         <v>10730.909</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -1533,7 +1550,7 @@
         <v>85.147999999999996</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -1553,7 +1570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -1573,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
@@ -1593,7 +1610,7 @@
         <v>3663.8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -1613,7 +1630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
@@ -1633,7 +1650,7 @@
         <v>10754.986999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
@@ -1653,7 +1670,7 @@
         <v>138.34200000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
@@ -1673,7 +1690,7 @@
         <v>37309.811999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
@@ -1693,7 +1710,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
@@ -1713,7 +1730,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
@@ -1733,7 +1750,7 @@
         <v>249.45699999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
@@ -1753,7 +1770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
@@ -1773,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
@@ -1793,7 +1810,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
@@ -1813,7 +1830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
@@ -1833,7 +1850,7 @@
         <v>149420.9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
@@ -1853,7 +1870,7 @@
         <v>18642.174999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
@@ -1873,7 +1890,7 @@
         <v>31357</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>52</v>
       </c>
@@ -1893,7 +1910,7 @@
         <v>3020</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
@@ -1913,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>54</v>
       </c>
@@ -1933,7 +1950,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>55</v>
       </c>
@@ -1953,7 +1970,7 @@
         <v>20007.008999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>56</v>
       </c>
@@ -1973,7 +1990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
@@ -1993,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
@@ -2013,7 +2030,7 @@
         <v>84008.865999999995</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
@@ -2033,7 +2050,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
@@ -2053,7 +2070,7 @@
         <v>4177.8990000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>61</v>
       </c>
@@ -2073,7 +2090,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
@@ -2093,7 +2110,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
@@ -2113,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
@@ -2133,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
@@ -2153,7 +2170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
@@ -2173,7 +2190,7 @@
         <v>871.92399999999998</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
@@ -2193,7 +2210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
@@ -2213,7 +2230,7 @@
         <v>1824.9770000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>69</v>
       </c>
@@ -2233,7 +2250,7 @@
         <v>305.00900000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>70</v>
       </c>
@@ -2253,7 +2270,7 @@
         <v>9014.1440000000002</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
@@ -2273,7 +2290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>72</v>
       </c>
@@ -2293,7 +2310,7 @@
         <v>14325.227999999999</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
@@ -2313,7 +2330,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>74</v>
       </c>
@@ -2333,7 +2350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
@@ -2353,7 +2370,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>76</v>
       </c>
@@ -2373,7 +2390,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
@@ -2393,7 +2410,7 @@
         <v>6395.45</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
@@ -2413,7 +2430,7 @@
         <v>566.029</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>79</v>
       </c>
@@ -2433,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>80</v>
       </c>
@@ -2453,7 +2470,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>81</v>
       </c>
@@ -2473,7 +2490,7 @@
         <v>610.10599999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>82</v>
       </c>
@@ -2493,7 +2510,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
@@ -2513,7 +2530,7 @@
         <v>2290.9870999999998</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
@@ -2533,7 +2550,7 @@
         <v>4127</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>85</v>
       </c>
@@ -2553,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>86</v>
       </c>
@@ -2573,7 +2590,7 @@
         <v>21.943000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>87</v>
       </c>
@@ -2593,7 +2610,7 @@
         <v>1526.819</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
@@ -2613,7 +2630,7 @@
         <v>1829.54</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>89</v>
       </c>
@@ -2633,7 +2650,7 @@
         <v>7112.808</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>90</v>
       </c>
@@ -2653,7 +2670,7 @@
         <v>1948.3320000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>91</v>
       </c>
@@ -2673,7 +2690,7 @@
         <v>1176.548</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
@@ -2693,7 +2710,7 @@
         <v>1364.279</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
@@ -2713,7 +2730,7 @@
         <v>71006.917000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
@@ -2733,7 +2750,7 @@
         <v>9605.7189999999991</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>95</v>
       </c>
@@ -2753,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>96</v>
       </c>
@@ -2773,7 +2790,7 @@
         <v>1393.2</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>97</v>
       </c>
@@ -2793,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>98</v>
       </c>
@@ -2813,7 +2830,7 @@
         <v>259.495</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>99</v>
       </c>
@@ -2833,7 +2850,7 @@
         <v>3865.7939999999999</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>100</v>
       </c>
@@ -2873,7 +2890,7 @@
         <v>4716.91</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>102</v>
       </c>
@@ -2893,7 +2910,7 @@
         <v>63648.377</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>103</v>
       </c>
@@ -2913,7 +2930,7 @@
         <v>11872.543</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>104</v>
       </c>
@@ -2933,7 +2950,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>105</v>
       </c>
@@ -2953,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>106</v>
       </c>
@@ -2973,7 +2990,7 @@
         <v>4024.7950000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>107</v>
       </c>
@@ -2993,7 +3010,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>108</v>
       </c>
@@ -3013,7 +3030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>109</v>
       </c>
@@ -3033,7 +3050,7 @@
         <v>19195.303</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>110</v>
       </c>
@@ -3053,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>111</v>
       </c>
@@ -3073,7 +3090,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>112</v>
       </c>
@@ -3093,7 +3110,7 @@
         <v>4918.4459999999999</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>113</v>
       </c>
@@ -3113,7 +3130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>114</v>
       </c>
@@ -3133,7 +3150,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>115</v>
       </c>
@@ -3153,7 +3170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>116</v>
       </c>
@@ -3173,7 +3190,7 @@
         <v>36893.392</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>117</v>
       </c>
@@ -3193,7 +3210,7 @@
         <v>7575.2</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>118</v>
       </c>
@@ -3213,7 +3230,7 @@
         <v>3725</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>119</v>
       </c>
@@ -3233,7 +3250,7 @@
         <v>4011.9404</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>131</v>
       </c>
@@ -3253,7 +3270,7 @@
         <v>79456.591</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>120</v>
       </c>
@@ -3273,7 +3290,7 @@
         <v>50.228000000000002</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>121</v>
       </c>
@@ -3293,7 +3310,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>122</v>
       </c>
@@ -3313,7 +3330,7 @@
         <v>28.748999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>123</v>
       </c>
@@ -3333,7 +3350,7 @@
         <v>21974.437999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>124</v>
       </c>
@@ -3353,7 +3370,7 @@
         <v>1886929.3875</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>125</v>
       </c>
@@ -3436,6 +3453,13 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A3:F128" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="South Africa"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="A130:N130"/>
     <mergeCell ref="A131:N131"/>

--- a/industry/input_data/steel/Worldsteel-totalproductionofcrudesteel.xlsx
+++ b/industry/input_data/steel/Worldsteel-totalproductionofcrudesteel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fraunhofer-my.sharepoint.com/personal/rakesh_etikala_narendar_iee_fraunhofer_de/Documents/Desktop/sectoral-energy-demands/industry/input_data/steel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_3352B0E1F3F105F010E720AC36A94142DD0FB1ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D8E9E39-47C6-41DB-8ACC-69454DABC7A9}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_3352B0E1F3F105F010E720AC36A94142DD0FB1ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBBB647C-AD30-4466-B410-8C18B8F655C2}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="22320" windowHeight="17770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="20" yWindow="740" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P1_crude_steel_total_pub" sheetId="1" r:id="rId1"/>
@@ -1510,7 +1510,7 @@
         <v>492.64400000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -2350,7 +2350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>594.61099999999999</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>101</v>
       </c>
@@ -3456,7 +3456,8 @@
   <autoFilter ref="A3:F128" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="South Africa"/>
+        <filter val="Egypt"/>
+        <filter val="Morocco"/>
       </filters>
     </filterColumn>
   </autoFilter>
